--- a/mountains_enriched_Oleksandr_Vasyleiko.xlsx
+++ b/mountains_enriched_Oleksandr_Vasyleiko.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4808</v>
+        <v>4807</v>
       </c>
     </row>
     <row r="4">

--- a/mountains_enriched_Oleksandr_Vasyleiko.xlsx
+++ b/mountains_enriched_Oleksandr_Vasyleiko.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,61 +436,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Everest</t>
+          <t>Mount Everest</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Nepal/China</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8848</v>
+        <v>8848.860000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mont Blanc</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Pakistan/China</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4807</v>
+        <v>8611</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Denali</t>
+          <t>Kangchenjunga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Nepal/India</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6190</v>
+        <v>8586</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Lhotse</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Nepal/China</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5895</v>
+        <v>8516</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Makalu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nepal/China</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8485</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cho Oyu</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nepal/China</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8188</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dhaulagiri</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8167</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Manaslu</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8163</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Nanga Parbat</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8126</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Annapurna</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8091</v>
       </c>
     </row>
   </sheetData>
